--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486912_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486912_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.004300000000001</v>
+        <v>7.0178</v>
       </c>
       <c r="E2" t="n">
-        <v>4.4294</v>
+        <v>2.8875</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5749</v>
+        <v>4.1303</v>
       </c>
       <c r="G2" t="n">
         <v>4.8022</v>
@@ -610,13 +610,13 @@
         <v>3.4908</v>
       </c>
       <c r="S2" t="n">
-        <v>3.8181</v>
+        <v>1.8316</v>
       </c>
       <c r="T2" t="n">
-        <v>2.3978</v>
+        <v>0.8559</v>
       </c>
       <c r="U2" t="n">
-        <v>1.4203</v>
+        <v>0.9757</v>
       </c>
       <c r="V2" t="n">
         <v>0.5893</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6715</v>
+        <v>3.8616</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9799</v>
+        <v>1.8438</v>
       </c>
       <c r="F3" t="n">
-        <v>1.6916</v>
+        <v>2.0177</v>
       </c>
       <c r="G3" t="n">
         <v>2.4185</v>
@@ -688,13 +688,13 @@
         <v>3.0801</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5417</v>
+        <v>-0.3516</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3097</v>
+        <v>-0.4457</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2319</v>
+        <v>0.0941</v>
       </c>
       <c r="V3" t="n">
         <v>1.1786</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9196</v>
+        <v>1.7634</v>
       </c>
       <c r="E4" t="n">
-        <v>-2.6348</v>
+        <v>0.7538</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5544</v>
+        <v>1.0097</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3093</v>
+        <v>-1.4269</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5934</v>
+        <v>-0.3375</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9026999999999999</v>
+        <v>-1.0893</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1</v>
+        <v>-1.4252</v>
       </c>
       <c r="K4" t="n">
-        <v>0.782</v>
+        <v>0.5485</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.882</v>
+        <v>-1.9737</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.2094</v>
+        <v>-0.0017</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1887</v>
+        <v>-0.886</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0207</v>
+        <v>0.8843</v>
       </c>
       <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-1.2321</v>
+      </c>
+      <c r="R4" t="n">
         <v>1.2321</v>
       </c>
-      <c r="Q4" t="n">
-        <v>-1.6427</v>
-      </c>
-      <c r="R4" t="n">
-        <v>2.8748</v>
-      </c>
       <c r="S4" t="n">
-        <v>-0.0032</v>
+        <v>0.1123</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1939</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1908</v>
+        <v>0.0195</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.078</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.6982</v>
+        <v>3.3182</v>
       </c>
       <c r="X4" t="n">
-        <v>0.6982</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8057</v>
+        <v>1.5503</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0331</v>
+        <v>-2.3597</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7725</v>
+        <v>3.9101</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.4269</v>
+        <v>-0.3093</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3375</v>
+        <v>0.5934</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.0893</v>
+        <v>-0.9026999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4252</v>
+        <v>-0.1</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5485</v>
+        <v>0.782</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9737</v>
+        <v>-0.882</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0017</v>
+        <v>-0.2094</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.886</v>
+        <v>-0.1887</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8843</v>
+        <v>-0.0207</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.2321</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.2321</v>
+        <v>-1.6427</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2321</v>
+        <v>2.8748</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8454</v>
+        <v>0.6276</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6278</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2176</v>
+        <v>0.5465</v>
       </c>
       <c r="V5" t="n">
-        <v>3.078</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>3.3182</v>
+        <v>-0.6982</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2402</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1592</v>
+        <v>0.1889</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1592</v>
+        <v>0.1889</v>
       </c>
       <c r="G6" t="n">
         <v>0.1395</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0198</v>
+        <v>0.0494</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.3528</v>
+        <v>-0.5306999999999999</v>
       </c>
       <c r="E7" t="n">
         <v>-2.041</v>
       </c>
       <c r="F7" t="n">
-        <v>1.6882</v>
+        <v>1.5103</v>
       </c>
       <c r="G7" t="n">
         <v>-2.4427</v>
@@ -1000,13 +1000,13 @@
         <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>1.098</v>
+        <v>0.9202</v>
       </c>
       <c r="T7" t="n">
         <v>0.4648</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6333</v>
+        <v>0.4554</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2402</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0339</v>
+        <v>-0.9475</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.3151</v>
+        <v>-1.288</v>
       </c>
       <c r="F8" t="n">
-        <v>0.2812</v>
+        <v>0.3405</v>
       </c>
       <c r="G8" t="n">
         <v>-1.181</v>
@@ -1078,13 +1078,13 @@
         <v>2.0534</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.0097</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3489</v>
+        <v>-0.3217</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2721</v>
+        <v>0.3314</v>
       </c>
       <c r="V8" t="n">
         <v>-1.4189</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.4378</v>
+        <v>-1.2705</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.2114</v>
+        <v>-1.6884</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7735</v>
+        <v>0.4178</v>
       </c>
       <c r="G9" t="n">
         <v>1.0754</v>
@@ -1156,13 +1156,13 @@
         <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1931</v>
+        <v>0.3604</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9068000000000001</v>
+        <v>-0.3837</v>
       </c>
       <c r="U9" t="n">
-        <v>1.0998</v>
+        <v>0.7441</v>
       </c>
       <c r="V9" t="n">
         <v>-2.7063</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.5038</v>
+        <v>-1.461</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4297</v>
+        <v>-1.2979</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0741</v>
+        <v>-0.163</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1733</v>
@@ -1234,13 +1234,13 @@
         <v>0.2053</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3305</v>
+        <v>-0.2877</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.527</v>
+        <v>-0.3952</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1965</v>
+        <v>0.1075</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.731</v>
+        <v>-1.8447</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3757</v>
+        <v>-2.519</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6447000000000001</v>
+        <v>0.6743</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0456</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5118</v>
+        <v>0.3981</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1704</v>
+        <v>0.027</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3414</v>
+        <v>0.371</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.4123</v>
+        <v>-2.2509</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.1929</v>
+        <v>-2.0611</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2194</v>
+        <v>-0.1898</v>
       </c>
       <c r="G12" t="n">
         <v>-1.0024</v>
@@ -1390,13 +1390,13 @@
         <v>0.2053</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3832</v>
+        <v>-0.2218</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2635</v>
+        <v>-0.1317</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1197</v>
+        <v>-0.0901</v>
       </c>
       <c r="V12" t="n">
         <v>0</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.088699999999999</v>
+        <v>6.076700000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>-8.758199999999999</v>
+        <v>-7.770000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13.8467</v>
+        <v>13.8468</v>
       </c>
       <c r="G13" t="n">
         <v>-0.1456000000000006</v>
@@ -1468,13 +1468,13 @@
         <v>17.454</v>
       </c>
       <c r="S13" t="n">
-        <v>2.46</v>
+        <v>3.4482</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1446</v>
+        <v>-0.1564</v>
       </c>
       <c r="U13" t="n">
-        <v>3.6048</v>
+        <v>3.6045</v>
       </c>
       <c r="V13" t="n">
         <v>0.7207000000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.526</v>
+        <v>5.8722</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3922</v>
+        <v>2.7646</v>
       </c>
       <c r="F14" t="n">
-        <v>3.1338</v>
+        <v>3.1076</v>
       </c>
       <c r="G14" t="n">
         <v>4.7728</v>
@@ -1546,13 +1546,13 @@
         <v>1.4374</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1023</v>
+        <v>0.4485</v>
       </c>
       <c r="T14" t="n">
-        <v>0.5461</v>
+        <v>-0.0815</v>
       </c>
       <c r="U14" t="n">
-        <v>0.5562</v>
+        <v>0.53</v>
       </c>
       <c r="V14" t="n">
         <v>0.2402</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5562</v>
+        <v>1.0026</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.928</v>
+        <v>-0.7188</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4842</v>
+        <v>1.7213</v>
       </c>
       <c r="G15" t="n">
         <v>0.7848000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>1.6427</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.5161</v>
+        <v>-0.0697</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3875</v>
+        <v>-0.1783</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1286</v>
+        <v>0.1086</v>
       </c>
       <c r="V15" t="n">
         <v>0.6982</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3428</v>
+        <v>0.9383</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0458</v>
+        <v>-1.4127</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3886</v>
+        <v>2.351</v>
       </c>
       <c r="G16" t="n">
-        <v>1.9093</v>
+        <v>-0.0002</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3618</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4525</v>
+        <v>-0.7104</v>
       </c>
       <c r="J16" t="n">
-        <v>3.0919</v>
+        <v>-1.1956</v>
       </c>
       <c r="K16" t="n">
-        <v>3.1053</v>
+        <v>0.1202</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.0134</v>
+        <v>-1.3158</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.1826</v>
+        <v>1.1954</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.7435</v>
+        <v>0.59</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.4391</v>
+        <v>0.6054</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.0801</v>
+        <v>1.8481</v>
       </c>
       <c r="Q16" t="n">
-        <v>-5.1336</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0534</v>
+        <v>1.8481</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3913</v>
+        <v>-0.4291</v>
       </c>
       <c r="T16" t="n">
-        <v>0.577</v>
+        <v>-0.4573</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8143</v>
+        <v>0.0283</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1224</v>
+        <v>-0.4805</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4189</v>
+        <v>0.2402</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.2965</v>
+        <v>-0.7207</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ECHEVERRIA FERNANDEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.048</v>
+        <v>0.2865</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6234</v>
+        <v>-0.5684</v>
       </c>
       <c r="F17" t="n">
-        <v>1.6713</v>
+        <v>0.8549</v>
       </c>
       <c r="G17" t="n">
-        <v>0.2336</v>
+        <v>-1.2896</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2466</v>
+        <v>-1.8816</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.013</v>
+        <v>0.592</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.7089</v>
+        <v>-0.2173</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0905</v>
+        <v>-1.3879</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6183999999999999</v>
+        <v>1.1706</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9425</v>
+        <v>-1.0723</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3371</v>
+        <v>-0.4937</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6054</v>
+        <v>-0.5786</v>
       </c>
       <c r="P17" t="n">
         <v>0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4374</v>
+        <v>2.4641</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1108</v>
+        <v>0.1046</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1122</v>
+        <v>-0.655</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0014</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.7072000000000001</v>
+        <v>1.0608</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>2.3573</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.7072000000000001</v>
+        <v>-1.2965</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>M. ECHEVERRIA FERNANDEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.092</v>
+        <v>0.1386</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9357</v>
+        <v>-1.8326</v>
       </c>
       <c r="F18" t="n">
-        <v>1.8437</v>
+        <v>1.9712</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0002</v>
+        <v>0.2336</v>
       </c>
       <c r="H18" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.2466</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.7104</v>
+        <v>-0.013</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.1956</v>
+        <v>-0.7089</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1202</v>
+        <v>-0.0905</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.3158</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>1.1954</v>
+        <v>0.9425</v>
       </c>
       <c r="N18" t="n">
-        <v>0.59</v>
+        <v>0.3371</v>
       </c>
       <c r="O18" t="n">
         <v>0.6054</v>
       </c>
       <c r="P18" t="n">
-        <v>1.8481</v>
+        <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8481</v>
+        <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4594</v>
+        <v>0.2015</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.9804</v>
+        <v>-0.097</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4791</v>
+        <v>0.2985</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4805</v>
+        <v>-0.7072000000000001</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.7207</v>
+        <v>-0.7072000000000001</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9897</v>
+        <v>-0.4819</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0914</v>
+        <v>-0.8826000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1017</v>
+        <v>0.4007</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.2896</v>
+        <v>1.9093</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8816</v>
+        <v>2.3618</v>
       </c>
       <c r="I19" t="n">
-        <v>0.592</v>
+        <v>-0.4525</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2173</v>
+        <v>3.0919</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.3879</v>
+        <v>3.1053</v>
       </c>
       <c r="L19" t="n">
-        <v>1.1706</v>
+        <v>-0.0134</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.0723</v>
+        <v>-1.1826</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.4937</v>
+        <v>-0.7435</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5786</v>
+        <v>-0.4391</v>
       </c>
       <c r="P19" t="n">
-        <v>0.4107</v>
+        <v>-3.0801</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-5.1336</v>
       </c>
       <c r="R19" t="n">
-        <v>2.4641</v>
+        <v>2.0534</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1716</v>
+        <v>0.5666</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.178</v>
+        <v>-0.2598</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0063</v>
+        <v>0.8264</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0608</v>
+        <v>0.1224</v>
       </c>
       <c r="W19" t="n">
-        <v>2.3573</v>
+        <v>1.4189</v>
       </c>
       <c r="X19" t="n">
         <v>-1.2965</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. TRAORE</t>
+          <t>K. CURFMAN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.158</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3381</v>
+        <v>-2.2236</v>
       </c>
       <c r="F20" t="n">
-        <v>0.1801</v>
+        <v>1.2412</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.669</v>
+        <v>-0.3163</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.1613</v>
+        <v>0.1814</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.5077</v>
+        <v>-0.4977</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3225</v>
+        <v>0.7874</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4409</v>
+        <v>0.5908</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1184</v>
+        <v>0.1966</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.3465</v>
+        <v>-1.1037</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7204</v>
+        <v>-0.4094</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6261</v>
+        <v>-0.6943</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.0267</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R20" t="n">
-        <v>1.0267</v>
+        <v>1.8481</v>
       </c>
       <c r="S20" t="n">
-        <v>1.7163</v>
+        <v>-0.3429</v>
       </c>
       <c r="T20" t="n">
-        <v>0.736</v>
+        <v>-0.8487</v>
       </c>
       <c r="U20" t="n">
-        <v>0.9804</v>
+        <v>0.5058</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1786</v>
+        <v>-0.1179</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.6982</v>
+        <v>-0.1088</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.4805</v>
+        <v>-0.008999999999999999</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>K. CURFMAN</t>
+          <t>S. TRAORE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.3318</v>
+        <v>-3.1867</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.9558</v>
+        <v>-3.0703</v>
       </c>
       <c r="F21" t="n">
-        <v>0.624</v>
+        <v>-0.1164</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3163</v>
+        <v>-1.669</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1814</v>
+        <v>-1.1613</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4977</v>
+        <v>-0.5077</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7874</v>
+        <v>-0.3225</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5908</v>
+        <v>-0.4409</v>
       </c>
       <c r="L21" t="n">
-        <v>0.1966</v>
+        <v>0.1184</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.1037</v>
+        <v>-1.3465</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4094</v>
+        <v>-0.7204</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.6943</v>
+        <v>-0.6261</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.2053</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.0534</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8481</v>
+        <v>1.0267</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.6923</v>
+        <v>0.6877</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.5809</v>
+        <v>0.0038</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.1113</v>
+        <v>0.6839</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1179</v>
+        <v>-1.1786</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.1088</v>
+        <v>-0.6982</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.008999999999999999</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-6.9902</v>
+        <v>-5.8865</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.3209</v>
+        <v>-5.9025</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6692</v>
+        <v>0.016</v>
       </c>
       <c r="G22" t="n">
         <v>-4.2799</v>
@@ -2170,13 +2170,13 @@
         <v>1.6427</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.9414</v>
+        <v>-0.8378</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.4492</v>
+        <v>-1.0308</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4923</v>
+        <v>0.1929</v>
       </c>
       <c r="V22" t="n">
         <v>-0.3581</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.0887</v>
+        <v>-2.2993</v>
       </c>
       <c r="E23" t="n">
         <v>-13.8469</v>
       </c>
       <c r="F23" t="n">
-        <v>8.7582</v>
+        <v>11.5475</v>
       </c>
       <c r="G23" t="n">
         <v>0.1455000000000002</v>
       </c>
       <c r="H23" t="n">
-        <v>2.2375</v>
+        <v>2.237500000000001</v>
       </c>
       <c r="I23" t="n">
         <v>-2.092</v>
@@ -2236,7 +2236,7 @@
         <v>-2.4533</v>
       </c>
       <c r="O23" t="n">
-        <v>0.01519999999999988</v>
+        <v>0.0152000000000001</v>
       </c>
       <c r="P23" t="n">
         <v>-2.0533</v>
@@ -2248,19 +2248,19 @@
         <v>15.4006</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.4601</v>
+        <v>0.3294</v>
       </c>
       <c r="T23" t="n">
-        <v>-3.6047</v>
+        <v>-3.6046</v>
       </c>
       <c r="U23" t="n">
-        <v>1.1445</v>
+        <v>3.934</v>
       </c>
       <c r="V23" t="n">
         <v>-0.7207</v>
       </c>
       <c r="W23" t="n">
-        <v>4.6282</v>
+        <v>4.628200000000001</v>
       </c>
       <c r="X23" t="n">
         <v>-5.349</v>
